--- a/static/data/exports/Retro_PB_AE_2012.xlsx
+++ b/static/data/exports/Retro_PB_AE_2012.xlsx
@@ -1590,11 +1590,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>22328</v>
+        <v>22339</v>
       </c>
       <c r="E16" t="n">
         <v>2779</v>
@@ -10290,11 +10290,11 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>22328</v>
+        <v>22339</v>
       </c>
       <c r="E132" t="n">
         <v>1212</v>
@@ -13965,11 +13965,11 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>22328</v>
+        <v>22339</v>
       </c>
       <c r="E181" t="n">
         <v>2208</v>
@@ -17031,20 +17031,20 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>1733948</v>
+        <v>1733947</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Tarsem Singh Daula</t>
+          <t>Balwant Singh Sultanpuri</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>BSP(A)</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>22303</v>
+        <v>22315</v>
       </c>
       <c r="E222" t="n">
         <v>1525</v>
@@ -17068,12 +17068,12 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Tarsem Singh Daula</t>
+          <t>Balwant Singh Sultanpuri</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>BSP(A)</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -17087,7 +17087,7 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="Q222" t="b">
         <v>0</v>
@@ -17106,20 +17106,20 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>1733947</v>
+        <v>1733948</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Balwant Singh Sultanpuri</t>
+          <t>Tarsem Singh Daula</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>BSP(A)</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>22315</v>
+        <v>22303</v>
       </c>
       <c r="E223" t="n">
         <v>1525</v>
@@ -17143,12 +17143,12 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Balwant Singh Sultanpuri</t>
+          <t>Tarsem Singh Daula</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>BSP(A)</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -17162,7 +17162,7 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="Q223" t="b">
         <v>0</v>
@@ -17331,20 +17331,20 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>1733951</v>
+        <v>1733952</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Gurmeet Singh</t>
+          <t>Ajit Singh</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SAD(A)</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>22306</v>
+        <v>22321</v>
       </c>
       <c r="E226" t="n">
         <v>363</v>
@@ -17368,12 +17368,12 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>Gurmeet Singh</t>
+          <t>Ajit Singh</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SAD(A)</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -17387,7 +17387,7 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="Q226" t="b">
         <v>0</v>
@@ -17406,20 +17406,20 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>1733952</v>
+        <v>1733951</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Ajit Singh</t>
+          <t>Gurmeet Singh</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>SAD(A)</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>22321</v>
+        <v>22306</v>
       </c>
       <c r="E227" t="n">
         <v>363</v>
@@ -17443,12 +17443,12 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Ajit Singh</t>
+          <t>Gurmeet Singh</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>SAD(A)</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -17462,7 +17462,7 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="Q227" t="b">
         <v>0</v>
@@ -18765,11 +18765,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>22328</v>
+        <v>22339</v>
       </c>
       <c r="E245" t="n">
         <v>2608</v>
@@ -28365,11 +28365,11 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>22328</v>
+        <v>22339</v>
       </c>
       <c r="E373" t="n">
         <v>4933</v>
@@ -29856,20 +29856,20 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>1735907</v>
+        <v>1735908</v>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Pala Singh</t>
+          <t>Davinder Singh</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SAD(A)</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>22306</v>
+        <v>22321</v>
       </c>
       <c r="E393" t="n">
         <v>187</v>
@@ -29893,12 +29893,12 @@
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>Pala Singh</t>
+          <t>Davinder Singh</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SAD(A)</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -29912,7 +29912,7 @@
         </is>
       </c>
       <c r="P393" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="Q393" t="b">
         <v>0</v>
@@ -29931,20 +29931,20 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>1735908</v>
+        <v>1735907</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Davinder Singh</t>
+          <t>Pala Singh</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>SAD(A)</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>22321</v>
+        <v>22306</v>
       </c>
       <c r="E394" t="n">
         <v>187</v>
@@ -29968,12 +29968,12 @@
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>Davinder Singh</t>
+          <t>Pala Singh</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>SAD(A)</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -29987,7 +29987,7 @@
         </is>
       </c>
       <c r="P394" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="Q394" t="b">
         <v>0</v>
@@ -30765,11 +30765,11 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>22328</v>
+        <v>22339</v>
       </c>
       <c r="E405" t="n">
         <v>3184</v>
@@ -37890,11 +37890,11 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>22328</v>
+        <v>22339</v>
       </c>
       <c r="E500" t="n">
         <v>1522</v>
@@ -56256,20 +56256,20 @@
     </row>
     <row r="745">
       <c r="A745" t="n">
-        <v>1740527</v>
+        <v>1740526</v>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Baldev Singh</t>
+          <t>Om Parkash</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>SAD(A)</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D745" t="n">
-        <v>22321</v>
+        <v>22306</v>
       </c>
       <c r="E745" t="n">
         <v>507</v>
@@ -56293,17 +56293,17 @@
       </c>
       <c r="K745" t="inlineStr">
         <is>
-          <t>Baldev Singh</t>
+          <t>Om Parkash</t>
         </is>
       </c>
       <c r="L745" t="inlineStr">
         <is>
-          <t>SAD(A)</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="N745" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="O745" t="inlineStr">
@@ -56312,7 +56312,7 @@
         </is>
       </c>
       <c r="P745" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="Q745" t="b">
         <v>0</v>
@@ -56331,20 +56331,20 @@
     </row>
     <row r="746">
       <c r="A746" t="n">
-        <v>1740526</v>
+        <v>1740527</v>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Om Parkash</t>
+          <t>Baldev Singh</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SAD(A)</t>
         </is>
       </c>
       <c r="D746" t="n">
-        <v>22306</v>
+        <v>22321</v>
       </c>
       <c r="E746" t="n">
         <v>507</v>
@@ -56368,17 +56368,17 @@
       </c>
       <c r="K746" t="inlineStr">
         <is>
-          <t>Om Parkash</t>
+          <t>Baldev Singh</t>
         </is>
       </c>
       <c r="L746" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SAD(A)</t>
         </is>
       </c>
       <c r="N746" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O746" t="inlineStr">
@@ -56387,7 +56387,7 @@
         </is>
       </c>
       <c r="P746" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="Q746" t="b">
         <v>0</v>
@@ -71490,11 +71490,11 @@
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D948" t="n">
-        <v>22328</v>
+        <v>22339</v>
       </c>
       <c r="E948" t="n">
         <v>1205</v>
@@ -78165,11 +78165,11 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1037" t="n">
-        <v>22328</v>
+        <v>22339</v>
       </c>
       <c r="E1037" t="n">
         <v>2068</v>
